--- a/BIIB.xlsx
+++ b/BIIB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D10051C-F814-4A29-8C41-79E388A6A93A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B969DF-5F47-45F9-80D3-255FF9E2F4B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18570" yWindow="1840" windowWidth="17760" windowHeight="18540" xr2:uid="{7CBEE6B4-8223-452C-B8C6-1EC2B28F2C97}"/>
+    <workbookView xWindow="350" yWindow="1040" windowWidth="19050" windowHeight="19840" xr2:uid="{7CBEE6B4-8223-452C-B8C6-1EC2B28F2C97}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="206">
   <si>
     <t>Price</t>
   </si>
@@ -672,13 +672,16 @@
   </si>
   <si>
     <t>Tofidence (tocilizumab, fka BIIB800)</t>
+  </si>
+  <si>
+    <t>Q226</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -712,12 +715,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -834,7 +831,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -884,7 +881,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1492,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="17">
-        <v>142</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
@@ -1510,10 +1506,10 @@
         <v>1</v>
       </c>
       <c r="J3" s="1">
-        <v>146</v>
+        <v>147.753998</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>125</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.25">
@@ -1532,7 +1528,7 @@
       </c>
       <c r="J4" s="1">
         <f>+J2*J3</f>
-        <v>20732</v>
+        <v>29846.307595999999</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.25">
@@ -1550,10 +1546,10 @@
         <v>3</v>
       </c>
       <c r="J5" s="1">
-        <v>2400</v>
+        <v>1285</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>125</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
@@ -1568,10 +1564,11 @@
         <v>4</v>
       </c>
       <c r="J6" s="1">
-        <v>3900</v>
+        <f>7290.3+800</f>
+        <v>8090.3</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>125</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.25">
@@ -1590,7 +1587,7 @@
       </c>
       <c r="J7" s="1">
         <f>+J4-J5+J6</f>
-        <v>22232</v>
+        <v>36651.607596000002</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.25">
@@ -1881,7 +1878,7 @@
       </c>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B35" s="31" t="s">
+      <c r="B35" t="s">
         <v>203</v>
       </c>
     </row>
@@ -5460,91 +5457,91 @@
         <v>10886.800000000003</v>
       </c>
       <c r="AM26" s="1">
-        <f>SUM(AM3:AM25)</f>
+        <f t="shared" ref="AM26:BH26" si="50">SUM(AM3:AM25)</f>
         <v>11379.800000000001</v>
       </c>
       <c r="AN26" s="1">
-        <f>SUM(AN3:AN25)</f>
+        <f t="shared" si="50"/>
         <v>10692.2</v>
       </c>
       <c r="AO26" s="1">
-        <f>SUM(AO3:AO25)</f>
+        <f t="shared" si="50"/>
         <v>8847.1999999999989</v>
       </c>
       <c r="AP26" s="1">
-        <f>SUM(AP3:AP25)</f>
+        <f t="shared" si="50"/>
         <v>7987.7000000000007</v>
       </c>
       <c r="AQ26" s="1">
-        <f>SUM(AQ3:AQ25)</f>
+        <f t="shared" si="50"/>
         <v>7215.8</v>
       </c>
       <c r="AR26" s="1">
-        <f>SUM(AR3:AR25)</f>
+        <f t="shared" si="50"/>
         <v>7195.6000000000013</v>
       </c>
       <c r="AS26" s="1">
-        <f>SUM(AS3:AS25)</f>
+        <f t="shared" si="50"/>
         <v>6968.6050000000014</v>
       </c>
       <c r="AT26" s="1">
-        <f>SUM(AT3:AT25)</f>
+        <f t="shared" si="50"/>
         <v>7032.232750000001</v>
       </c>
       <c r="AU26" s="1">
-        <f>SUM(AU3:AU25)</f>
+        <f t="shared" si="50"/>
         <v>6928.1579225000005</v>
       </c>
       <c r="AV26" s="1">
-        <f>SUM(AV3:AV25)</f>
+        <f t="shared" si="50"/>
         <v>6821.2230816750007</v>
       </c>
       <c r="AW26" s="1">
-        <f>SUM(AW3:AW25)</f>
+        <f t="shared" si="50"/>
         <v>6757.8189393002503</v>
       </c>
       <c r="AX26" s="1">
-        <f>SUM(AX3:AX25)</f>
+        <f t="shared" si="50"/>
         <v>6729.4276469330089</v>
       </c>
       <c r="AY26" s="1">
-        <f>SUM(AY3:AY25)</f>
+        <f t="shared" si="50"/>
         <v>6366.6278593389261</v>
       </c>
       <c r="AZ26" s="1">
-        <f>SUM(AZ3:AZ25)</f>
+        <f t="shared" si="50"/>
         <v>6116.1547000585215</v>
       </c>
       <c r="BA26" s="1">
-        <f>SUM(BA3:BA25)</f>
+        <f t="shared" si="50"/>
         <v>5915.9381224410245</v>
       </c>
       <c r="BB26" s="1">
-        <f>SUM(BB3:BB25)</f>
+        <f t="shared" si="50"/>
         <v>5758.7576177486408</v>
       </c>
       <c r="BC26" s="1">
-        <f>SUM(BC3:BC25)</f>
+        <f t="shared" si="50"/>
         <v>5638.6206349554377</v>
       </c>
       <c r="BD26" s="1">
-        <f>SUM(BD3:BD25)</f>
+        <f t="shared" si="50"/>
         <v>4460.5962943187424</v>
       </c>
       <c r="BE26" s="1">
-        <f>SUM(BE3:BE25)</f>
+        <f t="shared" si="50"/>
         <v>4269.6544104864279</v>
       </c>
       <c r="BF26" s="1">
-        <f>SUM(BF3:BF25)</f>
+        <f t="shared" si="50"/>
         <v>4198.6731243265613</v>
       </c>
       <c r="BG26" s="1">
-        <f>SUM(BG3:BG25)</f>
+        <f t="shared" si="50"/>
         <v>4158.4114316349969</v>
       </c>
       <c r="BH26" s="1">
-        <f>SUM(BH3:BH25)</f>
+        <f t="shared" si="50"/>
         <v>4137.8421969262108</v>
       </c>
     </row>
@@ -5643,67 +5640,67 @@
         <v>1339.5</v>
       </c>
       <c r="AS27" s="1">
-        <f t="shared" ref="AS27:BH27" si="50">+AR27*0.9</f>
+        <f t="shared" ref="AS27:BH27" si="51">+AR27*0.9</f>
         <v>1205.55</v>
       </c>
       <c r="AT27" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1084.9949999999999</v>
       </c>
       <c r="AU27" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>976.49549999999988</v>
       </c>
       <c r="AV27" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>878.8459499999999</v>
       </c>
       <c r="AW27" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>790.96135499999991</v>
       </c>
       <c r="AX27" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>711.86521949999997</v>
       </c>
       <c r="AY27" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>640.67869755000004</v>
       </c>
       <c r="AZ27" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>576.61082779500009</v>
       </c>
       <c r="BA27" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>518.94974501550007</v>
       </c>
       <c r="BB27" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>467.05477051395007</v>
       </c>
       <c r="BC27" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>420.34929346255507</v>
       </c>
       <c r="BD27" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>378.31436411629954</v>
       </c>
       <c r="BE27" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>340.48292770466958</v>
       </c>
       <c r="BF27" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>306.43463493420262</v>
       </c>
       <c r="BG27" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>275.79117144078236</v>
       </c>
       <c r="BH27" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>248.21205429670414</v>
       </c>
     </row>
@@ -5823,67 +5820,67 @@
         <v>392</v>
       </c>
       <c r="AS28" s="1">
-        <f t="shared" ref="AS28:BH28" si="51">+AR28*0.9</f>
+        <f t="shared" ref="AS28:BH28" si="52">+AR28*0.9</f>
         <v>352.8</v>
       </c>
       <c r="AT28" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>317.52000000000004</v>
       </c>
       <c r="AU28" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>285.76800000000003</v>
       </c>
       <c r="AV28" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>257.19120000000004</v>
       </c>
       <c r="AW28" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>231.47208000000003</v>
       </c>
       <c r="AX28" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>208.32487200000003</v>
       </c>
       <c r="AY28" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>187.49238480000002</v>
       </c>
       <c r="AZ28" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>168.74314632000002</v>
       </c>
       <c r="BA28" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>151.86883168800003</v>
       </c>
       <c r="BB28" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>136.68194851920003</v>
       </c>
       <c r="BC28" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>123.01375366728003</v>
       </c>
       <c r="BD28" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>110.71237830055203</v>
       </c>
       <c r="BE28" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>99.641140470496836</v>
       </c>
       <c r="BF28" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>89.67702642344716</v>
       </c>
       <c r="BG28" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>80.709323781102441</v>
       </c>
       <c r="BH28" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>72.638391402992198</v>
       </c>
     </row>
@@ -5973,67 +5970,67 @@
         <v>18.399999999999999</v>
       </c>
       <c r="AS29" s="1">
-        <f t="shared" ref="AS29:BH29" si="52">+AR29*0.9</f>
+        <f t="shared" ref="AS29:BH29" si="53">+AR29*0.9</f>
         <v>16.559999999999999</v>
       </c>
       <c r="AT29" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>14.904</v>
       </c>
       <c r="AU29" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>13.413600000000001</v>
       </c>
       <c r="AV29" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>12.072240000000001</v>
       </c>
       <c r="AW29" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>10.865016000000001</v>
       </c>
       <c r="AX29" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>9.7785144000000006</v>
       </c>
       <c r="AY29" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>8.8006629600000004</v>
       </c>
       <c r="AZ29" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>7.9205966640000005</v>
       </c>
       <c r="BA29" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>7.1285369976000004</v>
       </c>
       <c r="BB29" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>6.4156832978400002</v>
       </c>
       <c r="BC29" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>5.7741149680560007</v>
       </c>
       <c r="BD29" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>5.1967034712504008</v>
       </c>
       <c r="BE29" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>4.6770331241253604</v>
       </c>
       <c r="BF29" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>4.2093298117128244</v>
       </c>
       <c r="BG29" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>3.7883968305415419</v>
       </c>
       <c r="BH29" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>3.4095571474873876</v>
       </c>
     </row>
@@ -6212,67 +6209,67 @@
         <v>703.7</v>
       </c>
       <c r="AS31" s="1">
-        <f t="shared" ref="AS31:BH31" si="53">+AR31*0.9</f>
+        <f t="shared" ref="AS31:BH31" si="54">+AR31*0.9</f>
         <v>633.33000000000004</v>
       </c>
       <c r="AT31" s="1">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>569.99700000000007</v>
       </c>
       <c r="AU31" s="1">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>512.99730000000011</v>
       </c>
       <c r="AV31" s="1">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>461.6975700000001</v>
       </c>
       <c r="AW31" s="1">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>415.52781300000009</v>
       </c>
       <c r="AX31" s="1">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>373.9750317000001</v>
       </c>
       <c r="AY31" s="1">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>336.57752853000011</v>
       </c>
       <c r="AZ31" s="1">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>302.91977567700013</v>
       </c>
       <c r="BA31" s="1">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>272.6277981093001</v>
       </c>
       <c r="BB31" s="1">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>245.3650182983701</v>
       </c>
       <c r="BC31" s="1">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>220.82851646853311</v>
       </c>
       <c r="BD31" s="1">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>198.74566482167981</v>
       </c>
       <c r="BE31" s="1">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>178.87109833951183</v>
       </c>
       <c r="BF31" s="1">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>160.98398850556066</v>
       </c>
       <c r="BG31" s="1">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>144.88558965500459</v>
       </c>
       <c r="BH31" s="1">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>130.39703068950413</v>
       </c>
     </row>
@@ -6283,35 +6280,35 @@
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
       <c r="E32" s="14">
-        <f t="shared" ref="E32:L32" si="54">SUM(E26:E31)</f>
+        <f t="shared" ref="E32:L32" si="55">SUM(E26:E31)</f>
         <v>3376.099999999999</v>
       </c>
       <c r="F32" s="14">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>2852.5999999999995</v>
       </c>
       <c r="G32" s="14">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>2694.0000000000005</v>
       </c>
       <c r="H32" s="14">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>2774.9999999999995</v>
       </c>
       <c r="I32" s="14">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>2778.9000000000005</v>
       </c>
       <c r="J32" s="14">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>2734.0999999999995</v>
       </c>
       <c r="K32" s="14">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>2531.8000000000002</v>
       </c>
       <c r="L32" s="14">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>2589.1</v>
       </c>
       <c r="M32" s="14">
@@ -6327,31 +6324,31 @@
         <v>2463</v>
       </c>
       <c r="P32" s="14">
-        <f t="shared" ref="P32:Z32" si="55">SUM(P26:P31)</f>
+        <f t="shared" ref="P32:Z32" si="56">SUM(P26:P31)</f>
         <v>2456</v>
       </c>
       <c r="Q32" s="14">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>2530.3000000000006</v>
       </c>
       <c r="R32" s="14">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>2386.3000000000002</v>
       </c>
       <c r="S32" s="14">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>2290.5</v>
       </c>
       <c r="T32" s="14">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>2464.9000000000005</v>
       </c>
       <c r="U32" s="14">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>2465.7999999999997</v>
       </c>
       <c r="V32" s="14">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>2454.6999999999994</v>
       </c>
       <c r="W32" s="14">
@@ -6359,57 +6356,57 @@
         <v>2253.8000000000002</v>
       </c>
       <c r="X32" s="14">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>2399.92</v>
       </c>
       <c r="Y32" s="14">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>2429.1800000000003</v>
       </c>
       <c r="Z32" s="14">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>2406.6</v>
       </c>
       <c r="AA32" s="14"/>
       <c r="AB32" s="14"/>
       <c r="AF32" s="14">
-        <f t="shared" ref="AF32:AL32" si="56">SUM(AF26:AF31)</f>
+        <f t="shared" ref="AF32:AL32" si="57">SUM(AF26:AF31)</f>
         <v>1350.4</v>
       </c>
       <c r="AG32" s="14">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>1389.9</v>
       </c>
       <c r="AH32" s="14">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>9703.2999999999975</v>
       </c>
       <c r="AI32" s="14">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>10763.800000000003</v>
       </c>
       <c r="AJ32" s="14">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>11448.8</v>
       </c>
       <c r="AK32" s="14">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>12273.900000000001</v>
       </c>
       <c r="AL32" s="14">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>13452.900000000003</v>
       </c>
       <c r="AM32" s="14">
-        <f t="shared" ref="AM32:AO32" si="57">SUM(AM26:AM31)</f>
+        <f t="shared" ref="AM32:AO32" si="58">SUM(AM26:AM31)</f>
         <v>14377.900000000001</v>
       </c>
       <c r="AN32" s="14">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>13444.600000000002</v>
       </c>
       <c r="AO32" s="14">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>10981.999999999998</v>
       </c>
       <c r="AP32" s="14">
@@ -6425,67 +6422,67 @@
         <v>9675.9000000000033</v>
       </c>
       <c r="AS32" s="14">
-        <f t="shared" ref="AS32:BH32" si="58">SUM(AS26:AS31)</f>
+        <f t="shared" ref="AS32:BH32" si="59">SUM(AS26:AS31)</f>
         <v>9176.8450000000012</v>
       </c>
       <c r="AT32" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>9019.6487500000003</v>
       </c>
       <c r="AU32" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>8716.8323225000022</v>
       </c>
       <c r="AV32" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>8431.0300416750015</v>
       </c>
       <c r="AW32" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>8206.6452033002497</v>
       </c>
       <c r="AX32" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>8033.3712845330083</v>
       </c>
       <c r="AY32" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>7540.1771331789259</v>
       </c>
       <c r="AZ32" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>7172.3490465145214</v>
       </c>
       <c r="BA32" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>6866.5130342514249</v>
       </c>
       <c r="BB32" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>6614.2750383780003</v>
       </c>
       <c r="BC32" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>6408.5863135218615</v>
       </c>
       <c r="BD32" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>5153.5654050285239</v>
       </c>
       <c r="BE32" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>4893.3266101252311</v>
       </c>
       <c r="BF32" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>4759.9781040014841</v>
       </c>
       <c r="BG32" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>4663.5859133424274</v>
       </c>
       <c r="BH32" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>4592.4992304628986</v>
       </c>
     </row>
@@ -6587,11 +6584,11 @@
         <v>1805.2</v>
       </c>
       <c r="AO33" s="1">
-        <f t="shared" ref="AO33" si="59">SUM(G33:J33)</f>
+        <f t="shared" ref="AO33" si="60">SUM(G33:J33)</f>
         <v>2109.6999999999998</v>
       </c>
       <c r="AP33" s="1">
-        <f t="shared" ref="AP33" si="60">SUM(K33:N33)</f>
+        <f t="shared" ref="AP33" si="61">SUM(K33:N33)</f>
         <v>2278.3000000000002</v>
       </c>
       <c r="AQ33" s="1">
@@ -6603,67 +6600,67 @@
         <v>2136.8000000000002</v>
       </c>
       <c r="AS33" s="1">
-        <f t="shared" ref="AS33:BH33" si="61">+AS32-AS34</f>
+        <f t="shared" ref="AS33:BH33" si="62">+AS32-AS34</f>
         <v>1651.8321000000005</v>
       </c>
       <c r="AT33" s="1">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>1623.5367750000005</v>
       </c>
       <c r="AU33" s="1">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>1569.0298180500013</v>
       </c>
       <c r="AV33" s="1">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>1517.5854075015004</v>
       </c>
       <c r="AW33" s="1">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>1477.1961365940451</v>
       </c>
       <c r="AX33" s="1">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>1446.0068312159419</v>
       </c>
       <c r="AY33" s="1">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>1357.2318839722075</v>
       </c>
       <c r="AZ33" s="1">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>1291.0228283726146</v>
       </c>
       <c r="BA33" s="1">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>1235.9723461652566</v>
       </c>
       <c r="BB33" s="1">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>1190.5695069080402</v>
       </c>
       <c r="BC33" s="1">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>1153.545536433935</v>
       </c>
       <c r="BD33" s="1">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>927.64177290513453</v>
       </c>
       <c r="BE33" s="1">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>880.79878982254195</v>
       </c>
       <c r="BF33" s="1">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>856.79605872026741</v>
       </c>
       <c r="BG33" s="1">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>839.44546440163731</v>
       </c>
       <c r="BH33" s="1">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>826.64986148332218</v>
       </c>
     </row>
@@ -6674,55 +6671,55 @@
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
       <c r="E34" s="12">
-        <f t="shared" ref="E34:L34" si="62">+E32-E33</f>
+        <f t="shared" ref="E34:L34" si="63">+E32-E33</f>
         <v>2926.9999999999991</v>
       </c>
       <c r="F34" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>2361.9999999999995</v>
       </c>
       <c r="G34" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>2215.9000000000005</v>
       </c>
       <c r="H34" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>2315.2999999999997</v>
       </c>
       <c r="I34" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>2267.1000000000004</v>
       </c>
       <c r="J34" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>2073.9999999999995</v>
       </c>
       <c r="K34" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>1777.9</v>
       </c>
       <c r="L34" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>2105.1</v>
       </c>
       <c r="M34" s="12">
-        <f t="shared" ref="M34:Q34" si="63">+M32-M33</f>
+        <f t="shared" ref="M34:Q34" si="64">+M32-M33</f>
         <v>2039</v>
       </c>
       <c r="N34" s="12">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>1973.0999999999995</v>
       </c>
       <c r="O34" s="12">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>1800.2</v>
       </c>
       <c r="P34" s="12">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>1863.3</v>
       </c>
       <c r="Q34" s="12">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>1870.7000000000007</v>
       </c>
       <c r="R34" s="12">
@@ -6764,39 +6761,39 @@
       <c r="AA34" s="12"/>
       <c r="AB34" s="12"/>
       <c r="AH34" s="1">
-        <f t="shared" ref="AH34:AI34" si="64">+AH32-AH33</f>
+        <f t="shared" ref="AH34:AI34" si="65">+AH32-AH33</f>
         <v>8532.2999999999975</v>
       </c>
       <c r="AI34" s="1">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>9523.4000000000033</v>
       </c>
       <c r="AJ34" s="1">
-        <f t="shared" ref="AJ34:AP34" si="65">+AJ32-AJ33</f>
+        <f t="shared" ref="AJ34:AP34" si="66">+AJ32-AJ33</f>
         <v>9970.0999999999985</v>
       </c>
       <c r="AK34" s="1">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>10643.900000000001</v>
       </c>
       <c r="AL34" s="1">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>11636.600000000004</v>
       </c>
       <c r="AM34" s="1">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>12422.500000000002</v>
       </c>
       <c r="AN34" s="1">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>11639.400000000001</v>
       </c>
       <c r="AO34" s="1">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>8872.2999999999993</v>
       </c>
       <c r="AP34" s="1">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>8759.9000000000015</v>
       </c>
       <c r="AQ34" s="1">
@@ -6808,67 +6805,67 @@
         <v>7539.1000000000031</v>
       </c>
       <c r="AS34" s="1">
-        <f t="shared" ref="AS34:BH34" si="66">+AS32*0.82</f>
+        <f t="shared" ref="AS34:BH34" si="67">+AS32*0.82</f>
         <v>7525.0129000000006</v>
       </c>
       <c r="AT34" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>7396.1119749999998</v>
       </c>
       <c r="AU34" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>7147.8025044500009</v>
       </c>
       <c r="AV34" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>6913.4446341735011</v>
       </c>
       <c r="AW34" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>6729.4490667062046</v>
       </c>
       <c r="AX34" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>6587.3644533170664</v>
       </c>
       <c r="AY34" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>6182.9452492067185</v>
       </c>
       <c r="AZ34" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>5881.3262181419068</v>
       </c>
       <c r="BA34" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>5630.5406880861683</v>
       </c>
       <c r="BB34" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>5423.7055314699601</v>
       </c>
       <c r="BC34" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>5255.0407770879265</v>
       </c>
       <c r="BD34" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>4225.9236321233893</v>
       </c>
       <c r="BE34" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>4012.5278203026892</v>
       </c>
       <c r="BF34" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>3903.1820452812167</v>
       </c>
       <c r="BG34" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>3824.1404489407901</v>
       </c>
       <c r="BH34" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>3765.8493689795764</v>
       </c>
     </row>
@@ -6954,11 +6951,11 @@
         <v>3990.9</v>
       </c>
       <c r="AO35" s="1">
-        <f t="shared" ref="AO35:AO36" si="67">SUM(G35:J35)</f>
+        <f t="shared" ref="AO35:AO36" si="68">SUM(G35:J35)</f>
         <v>2501.2000000000003</v>
       </c>
       <c r="AP35" s="1">
-        <f t="shared" ref="AP35:AP36" si="68">SUM(K35:N35)</f>
+        <f t="shared" ref="AP35:AP36" si="69">SUM(K35:N35)</f>
         <v>2231.1000000000004</v>
       </c>
       <c r="AR35" s="1">
@@ -7064,11 +7061,11 @@
         <v>2504.5</v>
       </c>
       <c r="AO36" s="1">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>2674.3</v>
       </c>
       <c r="AP36" s="1">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>2403.6</v>
       </c>
       <c r="AQ36" s="1">
@@ -7080,67 +7077,67 @@
         <v>2339.5</v>
       </c>
       <c r="AS36" s="1">
-        <f t="shared" ref="AS36:BH36" si="69">+AR36*0.95</f>
+        <f t="shared" ref="AS36:BH36" si="70">+AR36*0.95</f>
         <v>2222.5250000000001</v>
       </c>
       <c r="AT36" s="1">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>2111.3987499999998</v>
       </c>
       <c r="AU36" s="1">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>2005.8288124999997</v>
       </c>
       <c r="AV36" s="1">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>1905.5373718749995</v>
       </c>
       <c r="AW36" s="1">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>1810.2605032812494</v>
       </c>
       <c r="AX36" s="1">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>1719.7474781171868</v>
       </c>
       <c r="AY36" s="1">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>1633.7601042113274</v>
       </c>
       <c r="AZ36" s="1">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>1552.072099000761</v>
       </c>
       <c r="BA36" s="1">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>1474.4684940507229</v>
       </c>
       <c r="BB36" s="1">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>1400.7450693481867</v>
       </c>
       <c r="BC36" s="1">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>1330.7078158807774</v>
       </c>
       <c r="BD36" s="1">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>1264.1724250867385</v>
       </c>
       <c r="BE36" s="1">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>1200.9638038324015</v>
       </c>
       <c r="BF36" s="1">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>1140.9156136407814</v>
       </c>
       <c r="BG36" s="1">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>1083.8698329587423</v>
       </c>
       <c r="BH36" s="1">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>1029.6763413108051</v>
       </c>
     </row>
@@ -7151,59 +7148,59 @@
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
       <c r="E37" s="12">
-        <f t="shared" ref="E37:L37" si="70">+E35+E36</f>
+        <f t="shared" ref="E37:L37" si="71">+E35+E36</f>
         <v>1714</v>
       </c>
       <c r="F37" s="12">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>2532.3000000000002</v>
       </c>
       <c r="G37" s="12">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>1109.2</v>
       </c>
       <c r="H37" s="12">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>1222.4000000000001</v>
       </c>
       <c r="I37" s="12">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>1356.5</v>
       </c>
       <c r="J37" s="12">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>1487.4</v>
       </c>
       <c r="K37" s="12">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>1186.5999999999999</v>
       </c>
       <c r="L37" s="12">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>1101.2</v>
       </c>
       <c r="M37" s="12">
-        <f t="shared" ref="M37:N37" si="71">+M35+M36</f>
+        <f t="shared" ref="M37:N37" si="72">+M35+M36</f>
         <v>1112.5</v>
       </c>
       <c r="N37" s="12">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>1234.4000000000001</v>
       </c>
       <c r="O37" s="12">
-        <f t="shared" ref="O37:R37" si="72">+O35+O36</f>
+        <f t="shared" ref="O37:R37" si="73">+O35+O36</f>
         <v>1175.5999999999999</v>
       </c>
       <c r="P37" s="12">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>1117.5999999999999</v>
       </c>
       <c r="Q37" s="12">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>1092.0999999999999</v>
       </c>
       <c r="R37" s="12">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>1156</v>
       </c>
       <c r="S37" s="12">
@@ -7223,49 +7220,49 @@
         <v>1200.7</v>
       </c>
       <c r="W37" s="12">
-        <f t="shared" ref="W37:Z37" si="73">+W35+W36</f>
+        <f t="shared" ref="W37:Z37" si="74">+W35+W36</f>
         <v>569.4</v>
       </c>
       <c r="X37" s="12">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>541.5</v>
       </c>
       <c r="Y37" s="12">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>556.1</v>
       </c>
       <c r="Z37" s="12">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>672.5</v>
       </c>
       <c r="AA37" s="12"/>
       <c r="AB37" s="12"/>
       <c r="AH37" s="1">
-        <f t="shared" ref="AH37:AJ37" si="74">+AH35+AH36</f>
+        <f t="shared" ref="AH37:AJ37" si="75">+AH35+AH36</f>
         <v>4125.7000000000007</v>
       </c>
       <c r="AI37" s="1">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>4125.8999999999996</v>
       </c>
       <c r="AJ37" s="1">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>3919.8999999999996</v>
       </c>
       <c r="AK37" s="1">
-        <f t="shared" ref="AK37:AL37" si="75">+AK35+AK36</f>
+        <f t="shared" ref="AK37:AL37" si="76">+AK35+AK36</f>
         <v>4187.5</v>
       </c>
       <c r="AL37" s="1">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>4703.5</v>
       </c>
       <c r="AM37" s="1">
-        <f t="shared" ref="AM37:AN37" si="76">+AM35+AM36</f>
+        <f t="shared" ref="AM37:AN37" si="77">+AM35+AM36</f>
         <v>4655.2999999999993</v>
       </c>
       <c r="AN37" s="1">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>6495.4</v>
       </c>
       <c r="AO37" s="1">
@@ -7277,75 +7274,75 @@
         <v>4634.7000000000007</v>
       </c>
       <c r="AQ37" s="1">
-        <f t="shared" ref="AQ37:BH37" si="77">+AQ35+AQ36</f>
+        <f t="shared" ref="AQ37:BH37" si="78">+AQ35+AQ36</f>
         <v>2283.4199999999996</v>
       </c>
       <c r="AR37" s="1">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>4269.3</v>
       </c>
       <c r="AS37" s="1">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>2222.5250000000001</v>
       </c>
       <c r="AT37" s="1">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>2111.3987499999998</v>
       </c>
       <c r="AU37" s="1">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>2005.8288124999997</v>
       </c>
       <c r="AV37" s="1">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1905.5373718749995</v>
       </c>
       <c r="AW37" s="1">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1810.2605032812494</v>
       </c>
       <c r="AX37" s="1">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1719.7474781171868</v>
       </c>
       <c r="AY37" s="1">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1633.7601042113274</v>
       </c>
       <c r="AZ37" s="1">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1552.072099000761</v>
       </c>
       <c r="BA37" s="1">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1474.4684940507229</v>
       </c>
       <c r="BB37" s="1">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1400.7450693481867</v>
       </c>
       <c r="BC37" s="1">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1330.7078158807774</v>
       </c>
       <c r="BD37" s="1">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1264.1724250867385</v>
       </c>
       <c r="BE37" s="1">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1200.9638038324015</v>
       </c>
       <c r="BF37" s="1">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1140.9156136407814</v>
       </c>
       <c r="BG37" s="1">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1083.8698329587423</v>
       </c>
       <c r="BH37" s="1">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1029.6763413108051</v>
       </c>
     </row>
@@ -7356,59 +7353,59 @@
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
       <c r="E38" s="12">
-        <f t="shared" ref="E38:L38" si="78">+E34-E37</f>
+        <f t="shared" ref="E38:L38" si="79">+E34-E37</f>
         <v>1212.9999999999991</v>
       </c>
       <c r="F38" s="12">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>-170.30000000000064</v>
       </c>
       <c r="G38" s="12">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>1106.7000000000005</v>
       </c>
       <c r="H38" s="12">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>1092.8999999999996</v>
       </c>
       <c r="I38" s="12">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>910.60000000000036</v>
       </c>
       <c r="J38" s="12">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>586.59999999999945</v>
       </c>
       <c r="K38" s="12">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>591.30000000000018</v>
       </c>
       <c r="L38" s="12">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>1003.8999999999999</v>
       </c>
       <c r="M38" s="12">
-        <f t="shared" ref="M38:N38" si="79">+M34-M37</f>
+        <f t="shared" ref="M38:N38" si="80">+M34-M37</f>
         <v>926.5</v>
       </c>
       <c r="N38" s="12">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>738.69999999999936</v>
       </c>
       <c r="O38" s="12">
-        <f t="shared" ref="O38:R38" si="80">+O34-O37</f>
+        <f t="shared" ref="O38:R38" si="81">+O34-O37</f>
         <v>624.60000000000014</v>
       </c>
       <c r="P38" s="12">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>745.7</v>
       </c>
       <c r="Q38" s="12">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>778.60000000000082</v>
       </c>
       <c r="R38" s="12">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>643.50000000000023</v>
       </c>
       <c r="S38" s="12">
@@ -7428,49 +7425,49 @@
         <v>713.49999999999932</v>
       </c>
       <c r="W38" s="12">
-        <f t="shared" ref="W38:Z38" si="81">+W34-W37</f>
+        <f t="shared" ref="W38:Z38" si="82">+W34-W37</f>
         <v>1188.5640000000003</v>
       </c>
       <c r="X38" s="12">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>1330.4376000000002</v>
       </c>
       <c r="Y38" s="12">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>1338.6604000000002</v>
       </c>
       <c r="Z38" s="12">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>1204.6479999999999</v>
       </c>
       <c r="AA38" s="12"/>
       <c r="AB38" s="12"/>
       <c r="AH38" s="1">
-        <f t="shared" ref="AH38:AJ38" si="82">+AH34-AH37</f>
+        <f t="shared" ref="AH38:AJ38" si="83">+AH34-AH37</f>
         <v>4406.5999999999967</v>
       </c>
       <c r="AI38" s="1">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>5397.5000000000036</v>
       </c>
       <c r="AJ38" s="1">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>6050.1999999999989</v>
       </c>
       <c r="AK38" s="1">
-        <f t="shared" ref="AK38:AL38" si="83">+AK34-AK37</f>
+        <f t="shared" ref="AK38:AL38" si="84">+AK34-AK37</f>
         <v>6456.4000000000015</v>
       </c>
       <c r="AL38" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>6933.100000000004</v>
       </c>
       <c r="AM38" s="1">
-        <f t="shared" ref="AM38:AN38" si="84">+AM34-AM37</f>
+        <f t="shared" ref="AM38:AN38" si="85">+AM34-AM37</f>
         <v>7767.2000000000025</v>
       </c>
       <c r="AN38" s="1">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>5144.0000000000018</v>
       </c>
       <c r="AO38" s="1">
@@ -7482,75 +7479,75 @@
         <v>4125.2000000000007</v>
       </c>
       <c r="AQ38" s="1">
-        <f t="shared" ref="AQ38:BH38" si="85">+AQ34-AQ37</f>
+        <f t="shared" ref="AQ38:BH38" si="86">+AQ34-AQ37</f>
         <v>6106.5740000000005</v>
       </c>
       <c r="AR38" s="1">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>3269.8000000000029</v>
       </c>
       <c r="AS38" s="1">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>5302.4879000000001</v>
       </c>
       <c r="AT38" s="1">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>5284.7132249999995</v>
       </c>
       <c r="AU38" s="1">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>5141.973691950001</v>
       </c>
       <c r="AV38" s="1">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>5007.9072622985013</v>
       </c>
       <c r="AW38" s="1">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>4919.1885634249556</v>
       </c>
       <c r="AX38" s="1">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>4867.6169751998796</v>
       </c>
       <c r="AY38" s="1">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>4549.1851449953911</v>
       </c>
       <c r="AZ38" s="1">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>4329.2541191411456</v>
       </c>
       <c r="BA38" s="1">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>4156.0721940354451</v>
       </c>
       <c r="BB38" s="1">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>4022.9604621217732</v>
       </c>
       <c r="BC38" s="1">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>3924.3329612071493</v>
       </c>
       <c r="BD38" s="1">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>2961.7512070366511</v>
       </c>
       <c r="BE38" s="1">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>2811.5640164702877</v>
       </c>
       <c r="BF38" s="1">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>2762.2664316404353</v>
       </c>
       <c r="BG38" s="1">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>2740.2706159820477</v>
       </c>
       <c r="BH38" s="1">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>2736.1730276687713</v>
       </c>
     </row>
@@ -7664,11 +7661,11 @@
         <v>730.3</v>
       </c>
       <c r="AO39" s="1">
-        <f t="shared" ref="AO39" si="86">SUM(G39:J39)</f>
+        <f t="shared" ref="AO39" si="87">SUM(G39:J39)</f>
         <v>-1050.0999999999999</v>
       </c>
       <c r="AP39" s="1">
-        <f t="shared" ref="AP39" si="87">SUM(K39:N39)</f>
+        <f t="shared" ref="AP39" si="88">SUM(K39:N39)</f>
         <v>-363</v>
       </c>
       <c r="AR39" s="1">
@@ -7683,63 +7680,63 @@
       <c r="C40" s="12"/>
       <c r="D40" s="12"/>
       <c r="E40" s="12">
-        <f t="shared" ref="E40:S40" si="88">+E38+E39</f>
+        <f t="shared" ref="E40:S40" si="89">+E38+E39</f>
         <v>1157.3999999999992</v>
       </c>
       <c r="F40" s="12">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>579.59999999999934</v>
       </c>
       <c r="G40" s="12">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>668.30000000000052</v>
       </c>
       <c r="H40" s="12">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>1077.6999999999996</v>
       </c>
       <c r="I40" s="12">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>428.90000000000038</v>
       </c>
       <c r="J40" s="12">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>471.79999999999944</v>
       </c>
       <c r="K40" s="12">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>210.70000000000016</v>
       </c>
       <c r="L40" s="12">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>1033.3</v>
       </c>
       <c r="M40" s="12">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>1027.8</v>
       </c>
       <c r="N40" s="12">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>625.59999999999934</v>
       </c>
       <c r="O40" s="12">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>555.20000000000016</v>
       </c>
       <c r="P40" s="12">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>760.40000000000009</v>
       </c>
       <c r="Q40" s="12">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>478.60000000000082</v>
       </c>
       <c r="R40" s="12">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>576.20000000000027</v>
       </c>
       <c r="S40" s="12">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>680.7</v>
       </c>
       <c r="T40" s="12">
@@ -7755,49 +7752,49 @@
         <v>641.79999999999927</v>
       </c>
       <c r="W40" s="12">
-        <f t="shared" ref="W40:Z40" si="89">+W38+W39</f>
+        <f t="shared" ref="W40:Z40" si="90">+W38+W39</f>
         <v>1116.8640000000003</v>
       </c>
       <c r="X40" s="12">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>1258.7376000000002</v>
       </c>
       <c r="Y40" s="12">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>1266.9604000000002</v>
       </c>
       <c r="Z40" s="12">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>1132.9479999999999</v>
       </c>
       <c r="AA40" s="12"/>
       <c r="AB40" s="12"/>
       <c r="AH40" s="1">
-        <f t="shared" ref="AH40:AK40" si="90">+AH38+AH39</f>
+        <f t="shared" ref="AH40:AK40" si="91">+AH38+AH39</f>
         <v>4380.7999999999965</v>
       </c>
       <c r="AI40" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>5273.8000000000038</v>
       </c>
       <c r="AJ40" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>5841.6999999999989</v>
       </c>
       <c r="AK40" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>6351.7000000000016</v>
       </c>
       <c r="AL40" s="1">
-        <f t="shared" ref="AL40:AN40" si="91">+AL38+AL39</f>
+        <f t="shared" ref="AL40:AN40" si="92">+AL38+AL39</f>
         <v>7129.100000000004</v>
       </c>
       <c r="AM40" s="1">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>8092.1000000000022</v>
       </c>
       <c r="AN40" s="1">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>5874.300000000002</v>
       </c>
       <c r="AO40" s="1">
@@ -7809,75 +7806,75 @@
         <v>3762.2000000000007</v>
       </c>
       <c r="AQ40" s="1">
-        <f t="shared" ref="AQ40:BH40" si="92">+AQ38+AQ39</f>
+        <f t="shared" ref="AQ40:BH40" si="93">+AQ38+AQ39</f>
         <v>6106.5740000000005</v>
       </c>
       <c r="AR40" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>2965.3000000000029</v>
       </c>
       <c r="AS40" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>5302.4879000000001</v>
       </c>
       <c r="AT40" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>5284.7132249999995</v>
       </c>
       <c r="AU40" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>5141.973691950001</v>
       </c>
       <c r="AV40" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>5007.9072622985013</v>
       </c>
       <c r="AW40" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>4919.1885634249556</v>
       </c>
       <c r="AX40" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>4867.6169751998796</v>
       </c>
       <c r="AY40" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>4549.1851449953911</v>
       </c>
       <c r="AZ40" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>4329.2541191411456</v>
       </c>
       <c r="BA40" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>4156.0721940354451</v>
       </c>
       <c r="BB40" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>4022.9604621217732</v>
       </c>
       <c r="BC40" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>3924.3329612071493</v>
       </c>
       <c r="BD40" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>2961.7512070366511</v>
       </c>
       <c r="BE40" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>2811.5640164702877</v>
       </c>
       <c r="BF40" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>2762.2664316404353</v>
       </c>
       <c r="BG40" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>2740.2706159820477</v>
       </c>
       <c r="BH40" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>2736.1730276687713</v>
       </c>
     </row>
@@ -7996,11 +7993,11 @@
         <v>1052.2</v>
       </c>
       <c r="AO41" s="1">
-        <f t="shared" ref="AO41" si="93">SUM(G41:J41)</f>
+        <f t="shared" ref="AO41" si="94">SUM(G41:J41)</f>
         <v>1007.3</v>
       </c>
       <c r="AP41" s="1">
-        <f t="shared" ref="AP41" si="94">SUM(K41:N41)</f>
+        <f t="shared" ref="AP41" si="95">SUM(K41:N41)</f>
         <v>544.9</v>
       </c>
       <c r="AQ41" s="1">
@@ -8012,67 +8009,67 @@
         <v>351.3</v>
       </c>
       <c r="AS41" s="1">
-        <f t="shared" ref="AS41:BH41" si="95">+AS40*0.2</f>
+        <f t="shared" ref="AS41:BH41" si="96">+AS40*0.2</f>
         <v>1060.49758</v>
       </c>
       <c r="AT41" s="1">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>1056.9426449999999</v>
       </c>
       <c r="AU41" s="1">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>1028.3947383900002</v>
       </c>
       <c r="AV41" s="1">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>1001.5814524597004</v>
       </c>
       <c r="AW41" s="1">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>983.83771268499117</v>
       </c>
       <c r="AX41" s="1">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>973.52339503997598</v>
       </c>
       <c r="AY41" s="1">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>909.83702899907826</v>
       </c>
       <c r="AZ41" s="1">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>865.85082382822918</v>
       </c>
       <c r="BA41" s="1">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>831.2144388070891</v>
       </c>
       <c r="BB41" s="1">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>804.59209242435463</v>
       </c>
       <c r="BC41" s="1">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>784.86659224142988</v>
       </c>
       <c r="BD41" s="1">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>592.35024140733026</v>
       </c>
       <c r="BE41" s="1">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>562.31280329405752</v>
       </c>
       <c r="BF41" s="1">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>552.45328632808707</v>
       </c>
       <c r="BG41" s="1">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>548.05412319640959</v>
       </c>
       <c r="BH41" s="1">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>547.23460553375423</v>
       </c>
     </row>
@@ -8081,35 +8078,35 @@
         <v>66</v>
       </c>
       <c r="E42" s="12">
-        <f t="shared" ref="E42:R42" si="96">+E40-E41</f>
+        <f t="shared" ref="E42:R42" si="97">+E40-E41</f>
         <v>901.09999999999923</v>
       </c>
       <c r="F42" s="12">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>584.59999999999934</v>
       </c>
       <c r="G42" s="12">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>611.50000000000057</v>
       </c>
       <c r="H42" s="12">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>125.89999999999964</v>
       </c>
       <c r="I42" s="12">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>467.0000000000004</v>
       </c>
       <c r="J42" s="12">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>434.99999999999943</v>
       </c>
       <c r="K42" s="12">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>167.10000000000014</v>
       </c>
       <c r="L42" s="12">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>822.5</v>
       </c>
       <c r="M42" s="12">
@@ -8117,23 +8114,23 @@
         <v>791.59999999999991</v>
       </c>
       <c r="N42" s="12">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>571.29999999999939</v>
       </c>
       <c r="O42" s="12">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>504.50000000000017</v>
       </c>
       <c r="P42" s="12">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>651.50000000000011</v>
       </c>
       <c r="Q42" s="12">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>405.70000000000084</v>
       </c>
       <c r="R42" s="12">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>533.50000000000023</v>
       </c>
       <c r="S42" s="12">
@@ -8153,130 +8150,130 @@
         <v>571.99999999999932</v>
       </c>
       <c r="W42" s="12">
-        <f t="shared" ref="W42:Z42" si="97">+W40-W41</f>
+        <f t="shared" ref="W42:Z42" si="98">+W40-W41</f>
         <v>949.33440000000019</v>
       </c>
       <c r="X42" s="12">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>1069.9269600000002</v>
       </c>
       <c r="Y42" s="12">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>1076.9163400000002</v>
       </c>
       <c r="Z42" s="12">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>963.00579999999991</v>
       </c>
       <c r="AA42" s="12"/>
       <c r="AB42" s="12"/>
       <c r="AC42" s="12"/>
       <c r="AH42" s="1">
-        <f t="shared" ref="AH42:AI42" si="98">+AH40-AH41</f>
+        <f t="shared" ref="AH42:AI42" si="99">+AH40-AH41</f>
         <v>3384.0999999999967</v>
       </c>
       <c r="AI42" s="1">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>4066.0000000000036</v>
       </c>
       <c r="AJ42" s="1">
-        <f t="shared" ref="AJ42:AQ42" si="99">+AJ40-AJ41</f>
+        <f t="shared" ref="AJ42:AQ42" si="100">+AJ40-AJ41</f>
         <v>3251.9999999999991</v>
       </c>
       <c r="AK42" s="1">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>3762.0000000000018</v>
       </c>
       <c r="AL42" s="1">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>5660.2000000000044</v>
       </c>
       <c r="AM42" s="1">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>6854.7000000000025</v>
       </c>
       <c r="AN42" s="1">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>4822.1000000000022</v>
       </c>
       <c r="AO42" s="1">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>1639.3999999999994</v>
       </c>
       <c r="AP42" s="1">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>3217.3000000000006</v>
       </c>
       <c r="AQ42" s="1">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>4885.2592000000004</v>
       </c>
       <c r="AR42" s="1">
-        <f t="shared" ref="AR42:BH42" si="100">+AR40-AR41</f>
+        <f t="shared" ref="AR42:BH42" si="101">+AR40-AR41</f>
         <v>2614.0000000000027</v>
       </c>
       <c r="AS42" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>4241.9903199999999</v>
       </c>
       <c r="AT42" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>4227.7705799999994</v>
       </c>
       <c r="AU42" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>4113.5789535600006</v>
       </c>
       <c r="AV42" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>4006.325809838801</v>
       </c>
       <c r="AW42" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>3935.3508507399647</v>
       </c>
       <c r="AX42" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>3894.0935801599035</v>
       </c>
       <c r="AY42" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>3639.348115996313</v>
       </c>
       <c r="AZ42" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>3463.4032953129163</v>
       </c>
       <c r="BA42" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>3324.8577552283559</v>
       </c>
       <c r="BB42" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>3218.3683696974185</v>
       </c>
       <c r="BC42" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>3139.4663689657195</v>
       </c>
       <c r="BD42" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>2369.400965629321</v>
       </c>
       <c r="BE42" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>2249.2512131762301</v>
       </c>
       <c r="BF42" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>2209.8131453123483</v>
       </c>
       <c r="BG42" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>2192.2164927856384</v>
       </c>
       <c r="BH42" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>2188.9384221350169</v>
       </c>
       <c r="BI42" s="1">
@@ -8284,347 +8281,347 @@
         <v>2167.0490379136668</v>
       </c>
       <c r="BJ42" s="1">
-        <f t="shared" ref="BJ42:DU42" si="101">+BI42*(1+$BK$45)</f>
+        <f t="shared" ref="BJ42:DU42" si="102">+BI42*(1+$BK$45)</f>
         <v>2145.3785475345303</v>
       </c>
       <c r="BK42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>2123.924762059185</v>
       </c>
       <c r="BL42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>2102.6855144385931</v>
       </c>
       <c r="BM42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>2081.6586592942072</v>
       </c>
       <c r="BN42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>2060.8420727012649</v>
       </c>
       <c r="BO42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>2040.2336519742523</v>
       </c>
       <c r="BP42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>2019.8313154545099</v>
       </c>
       <c r="BQ42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1999.6330022999648</v>
       </c>
       <c r="BR42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1979.6366722769651</v>
       </c>
       <c r="BS42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1959.8403055541955</v>
       </c>
       <c r="BT42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1940.2419024986536</v>
       </c>
       <c r="BU42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1920.8394834736671</v>
       </c>
       <c r="BV42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1901.6310886389304</v>
       </c>
       <c r="BW42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1882.6147777525409</v>
       </c>
       <c r="BX42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1863.7886299750155</v>
       </c>
       <c r="BY42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1845.1507436752654</v>
       </c>
       <c r="BZ42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1826.6992362385126</v>
       </c>
       <c r="CA42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1808.4322438761276</v>
       </c>
       <c r="CB42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1790.3479214373663</v>
       </c>
       <c r="CC42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1772.4444422229926</v>
       </c>
       <c r="CD42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1754.7199978007627</v>
       </c>
       <c r="CE42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1737.172797822755</v>
       </c>
       <c r="CF42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1719.8010698445275</v>
       </c>
       <c r="CG42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1702.6030591460822</v>
       </c>
       <c r="CH42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1685.5770285546214</v>
       </c>
       <c r="CI42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1668.7212582690752</v>
       </c>
       <c r="CJ42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1652.0340456863844</v>
       </c>
       <c r="CK42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1635.5137052295206</v>
       </c>
       <c r="CL42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1619.1585681772253</v>
       </c>
       <c r="CM42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1602.9669824954531</v>
       </c>
       <c r="CN42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1586.9373126704986</v>
       </c>
       <c r="CO42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1571.0679395437935</v>
       </c>
       <c r="CP42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1555.3572601483556</v>
       </c>
       <c r="CQ42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1539.803687546872</v>
       </c>
       <c r="CR42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1524.4056506714032</v>
       </c>
       <c r="CS42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1509.1615941646892</v>
       </c>
       <c r="CT42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1494.0699782230422</v>
       </c>
       <c r="CU42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1479.1292784408117</v>
       </c>
       <c r="CV42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1464.3379856564036</v>
       </c>
       <c r="CW42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1449.6946057998396</v>
       </c>
       <c r="CX42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1435.1976597418411</v>
       </c>
       <c r="CY42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1420.8456831444228</v>
       </c>
       <c r="CZ42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1406.6372263129786</v>
       </c>
       <c r="DA42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1392.5708540498488</v>
       </c>
       <c r="DB42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1378.6451455093502</v>
       </c>
       <c r="DC42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1364.8586940542566</v>
       </c>
       <c r="DD42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1351.210107113714</v>
       </c>
       <c r="DE42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1337.6980060425769</v>
       </c>
       <c r="DF42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1324.3210259821512</v>
       </c>
       <c r="DG42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1311.0778157223297</v>
       </c>
       <c r="DH42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1297.9670375651062</v>
       </c>
       <c r="DI42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1284.9873671894552</v>
       </c>
       <c r="DJ42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1272.1374935175606</v>
       </c>
       <c r="DK42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1259.416118582385</v>
       </c>
       <c r="DL42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1246.8219573965612</v>
       </c>
       <c r="DM42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1234.3537378225956</v>
       </c>
       <c r="DN42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1222.0102004443695</v>
       </c>
       <c r="DO42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1209.7900984399257</v>
       </c>
       <c r="DP42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1197.6921974555264</v>
       </c>
       <c r="DQ42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1185.7152754809711</v>
       </c>
       <c r="DR42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1173.8581227261614</v>
       </c>
       <c r="DS42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1162.1195414988997</v>
       </c>
       <c r="DT42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1150.4983460839107</v>
       </c>
       <c r="DU42" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>1138.9933626230716</v>
       </c>
       <c r="DV42" s="1">
-        <f t="shared" ref="DV42:EQ42" si="102">+DU42*(1+$BK$45)</f>
+        <f t="shared" ref="DV42:EQ42" si="103">+DU42*(1+$BK$45)</f>
         <v>1127.6034289968409</v>
       </c>
       <c r="DW42" s="1">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>1116.3273947068724</v>
       </c>
       <c r="DX42" s="1">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>1105.1641207598036</v>
       </c>
       <c r="DY42" s="1">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>1094.1124795522055</v>
       </c>
       <c r="DZ42" s="1">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>1083.1713547566835</v>
       </c>
       <c r="EA42" s="1">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>1072.3396412091167</v>
       </c>
       <c r="EB42" s="1">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>1061.6162447970255</v>
       </c>
       <c r="EC42" s="1">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>1051.0000823490552</v>
       </c>
       <c r="ED42" s="1">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>1040.4900815255646</v>
       </c>
       <c r="EE42" s="1">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>1030.085180710309</v>
       </c>
       <c r="EF42" s="1">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>1019.784328903206</v>
       </c>
       <c r="EG42" s="1">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>1009.5864856141739</v>
       </c>
       <c r="EH42" s="1">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>999.49062075803215</v>
       </c>
       <c r="EI42" s="1">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>989.49571455045179</v>
       </c>
       <c r="EJ42" s="1">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>979.60075740494722</v>
       </c>
       <c r="EK42" s="1">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>969.80474983089778</v>
       </c>
       <c r="EL42" s="1">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>960.10670233258884</v>
       </c>
       <c r="EM42" s="1">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>950.50563530926297</v>
       </c>
       <c r="EN42" s="1">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>941.00057895617033</v>
       </c>
       <c r="EO42" s="1">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>931.59057316660858</v>
       </c>
       <c r="EP42" s="1">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>922.27466743494244</v>
       </c>
       <c r="EQ42" s="1">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>913.05192076059302</v>
       </c>
     </row>
@@ -8633,201 +8630,201 @@
         <v>1</v>
       </c>
       <c r="E43" s="15">
-        <f t="shared" ref="E43:L43" si="103">+E42/E44</f>
+        <f t="shared" ref="E43:L43" si="104">+E42/E44</f>
         <v>5.7321882951653897</v>
       </c>
       <c r="F43" s="15">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>3.796103896103892</v>
       </c>
       <c r="G43" s="15">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>4.0151017728168128</v>
       </c>
       <c r="H43" s="15">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.83877415056628679</v>
       </c>
       <c r="I43" s="15">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>3.1426648721399757</v>
       </c>
       <c r="J43" s="15">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>2.9491525423728775</v>
       </c>
       <c r="K43" s="15">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>1.1321138211382122</v>
       </c>
       <c r="L43" s="15">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>5.625854993160055</v>
       </c>
       <c r="M43" s="15">
-        <f t="shared" ref="M43:V43" si="104">+M42/M44</f>
+        <f t="shared" ref="M43:V43" si="105">+M42/M44</f>
         <v>5.4668508287292807</v>
       </c>
       <c r="N43" s="15">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>3.9345730027548171</v>
       </c>
       <c r="O43" s="15">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>3.4745179063360898</v>
       </c>
       <c r="P43" s="15">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>4.4776632302405508</v>
       </c>
       <c r="Q43" s="15">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>2.801795580110503</v>
       </c>
       <c r="R43" s="15">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>3.661633493479755</v>
       </c>
       <c r="S43" s="15">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>4.1761480466072651</v>
       </c>
       <c r="T43" s="15">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>5.1802604523646361</v>
       </c>
       <c r="U43" s="15">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>4.6331279945242967</v>
       </c>
       <c r="V43" s="15">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>3.9151266255989001</v>
       </c>
       <c r="W43" s="15">
-        <f t="shared" ref="W43:Z43" si="105">+W42/W44</f>
+        <f t="shared" ref="W43:Z43" si="106">+W42/W44</f>
         <v>6.4978398357289544</v>
       </c>
       <c r="X43" s="15">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>7.3232509240246424</v>
       </c>
       <c r="Y43" s="15">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>7.3710906228610558</v>
       </c>
       <c r="Z43" s="15">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>6.5914154688569466</v>
       </c>
       <c r="AA43" s="15"/>
       <c r="AB43" s="15"/>
       <c r="AH43" s="17">
-        <f t="shared" ref="AH43:AI43" si="106">+AH42/AH44</f>
+        <f t="shared" ref="AH43:AI43" si="107">+AH42/AH44</f>
         <v>14.266863406408081</v>
       </c>
       <c r="AI43" s="17">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>17.586505190311435</v>
       </c>
       <c r="AJ43" s="17">
-        <f t="shared" ref="AJ43:AQ43" si="107">+AJ42/AJ44</f>
+        <f t="shared" ref="AJ43:AQ43" si="108">+AJ42/AJ44</f>
         <v>14.862888482632536</v>
       </c>
       <c r="AK43" s="17">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>17.661971830985923</v>
       </c>
       <c r="AL43" s="17">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>27.570384802727734</v>
       </c>
       <c r="AM43" s="17">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>36.577908217716129</v>
       </c>
       <c r="AN43" s="17">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>29.895226286422826</v>
       </c>
       <c r="AO43" s="17">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>10.956725146198826</v>
       </c>
       <c r="AP43" s="17">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>22.043850633778696</v>
       </c>
       <c r="AQ43" s="17">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>33.472142514559785</v>
       </c>
       <c r="AR43" s="17">
-        <f t="shared" ref="AR43:BH43" si="108">+AR42/AR44</f>
+        <f t="shared" ref="AR43:BH43" si="109">+AR42/AR44</f>
         <v>17.904109589041113</v>
       </c>
       <c r="AS43" s="17">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>29.054728219178081</v>
       </c>
       <c r="AT43" s="17">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>28.957332739726024</v>
       </c>
       <c r="AU43" s="17">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>28.1751983120548</v>
       </c>
       <c r="AV43" s="17">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>27.440587738621925</v>
       </c>
       <c r="AW43" s="17">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>26.954457881780581</v>
       </c>
       <c r="AX43" s="17">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>26.671873836711669</v>
       </c>
       <c r="AY43" s="17">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>24.927041890385706</v>
       </c>
       <c r="AZ43" s="17">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>23.721940378855592</v>
       </c>
       <c r="BA43" s="17">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>22.77299832348189</v>
       </c>
       <c r="BB43" s="17">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>22.043618970530265</v>
       </c>
       <c r="BC43" s="17">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>21.50319430798438</v>
       </c>
       <c r="BD43" s="17">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>16.228773737187129</v>
       </c>
       <c r="BE43" s="17">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>15.405830227234453</v>
       </c>
       <c r="BF43" s="17">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>15.135706474742111</v>
       </c>
       <c r="BG43" s="17">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>15.01518145743588</v>
       </c>
       <c r="BH43" s="17">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>14.992728918732993</v>
       </c>
     </row>
@@ -8945,67 +8942,67 @@
         <v>146</v>
       </c>
       <c r="AS44" s="1">
-        <f t="shared" ref="AS44:BH44" si="109">+AR44</f>
+        <f t="shared" ref="AS44:BH44" si="110">+AR44</f>
         <v>146</v>
       </c>
       <c r="AT44" s="1">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>146</v>
       </c>
       <c r="AU44" s="1">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>146</v>
       </c>
       <c r="AV44" s="1">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>146</v>
       </c>
       <c r="AW44" s="1">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>146</v>
       </c>
       <c r="AX44" s="1">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>146</v>
       </c>
       <c r="AY44" s="1">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>146</v>
       </c>
       <c r="AZ44" s="1">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>146</v>
       </c>
       <c r="BA44" s="1">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>146</v>
       </c>
       <c r="BB44" s="1">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>146</v>
       </c>
       <c r="BC44" s="1">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>146</v>
       </c>
       <c r="BD44" s="1">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>146</v>
       </c>
       <c r="BE44" s="1">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>146</v>
       </c>
       <c r="BF44" s="1">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>146</v>
       </c>
       <c r="BG44" s="1">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>146</v>
       </c>
       <c r="BH44" s="1">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>146</v>
       </c>
     </row>
@@ -9036,101 +9033,101 @@
       <c r="G47" s="21"/>
       <c r="H47" s="21"/>
       <c r="I47" s="22">
-        <f t="shared" ref="I47:O47" si="110">+I32/E32-1</f>
+        <f t="shared" ref="I47:O47" si="111">+I32/E32-1</f>
         <v>-0.1768904949497937</v>
       </c>
       <c r="J47" s="22">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>-4.1541050269929158E-2</v>
       </c>
       <c r="K47" s="22">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>-6.0207869339272579E-2</v>
       </c>
       <c r="L47" s="22">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>-6.6990990990990817E-2</v>
       </c>
       <c r="M47" s="22">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>-9.7304688905682335E-2</v>
       </c>
       <c r="N47" s="22">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>-6.9529278373139269E-2</v>
       </c>
       <c r="O47" s="22">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>-2.7174342365115844E-2</v>
       </c>
       <c r="P47" s="22">
-        <f t="shared" ref="P47:Z47" si="111">+P32/L32-1</f>
+        <f t="shared" ref="P47:Z47" si="112">+P32/L32-1</f>
         <v>-5.1407825112973593E-2</v>
       </c>
       <c r="Q47" s="22">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>8.6904524616306933E-3</v>
       </c>
       <c r="R47" s="22">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>-6.1988993710691553E-2</v>
       </c>
       <c r="S47" s="22">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>-7.0036540803897651E-2</v>
       </c>
       <c r="T47" s="22">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>3.6237785016288715E-3</v>
       </c>
       <c r="U47" s="22">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>-2.5491048492274015E-2</v>
       </c>
       <c r="V47" s="22">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>2.8663621506096915E-2</v>
       </c>
       <c r="W47" s="22">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>-1.6022702466710226E-2</v>
       </c>
       <c r="X47" s="22">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>-2.6362124224106664E-2</v>
       </c>
       <c r="Y47" s="22">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>-1.4851163922458999E-2</v>
       </c>
       <c r="Z47" s="22">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>-1.9595062533099505E-2</v>
       </c>
       <c r="AA47" s="22"/>
       <c r="AB47" s="22"/>
       <c r="AH47" s="24">
-        <f t="shared" ref="AH47:AM47" si="112">+AH32/AG32-1</f>
+        <f t="shared" ref="AH47:AM47" si="113">+AH32/AG32-1</f>
         <v>5.9812936182459149</v>
       </c>
       <c r="AI47" s="24">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>0.10929271484958791</v>
       </c>
       <c r="AJ47" s="24">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>6.3639235214329126E-2</v>
       </c>
       <c r="AK47" s="24">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>7.2068688421494054E-2</v>
       </c>
       <c r="AL47" s="24">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>9.6057487840051081E-2</v>
       </c>
       <c r="AM47" s="24">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>6.8758408967583007E-2</v>
       </c>
       <c r="AN47" s="24">
@@ -9138,83 +9135,83 @@
         <v>-6.4912122076241974E-2</v>
       </c>
       <c r="AO47" s="24">
-        <f t="shared" ref="AO47:BH47" si="113">+AO32/AN32-1</f>
+        <f t="shared" ref="AO47:BH47" si="114">+AO32/AN32-1</f>
         <v>-0.18316647575978484</v>
       </c>
       <c r="AP47" s="24">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>5.1174649426337648E-3</v>
       </c>
       <c r="AQ47" s="24">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-7.3064448913772284E-2</v>
       </c>
       <c r="AR47" s="24">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-5.4321373769754544E-2</v>
       </c>
       <c r="AS47" s="24">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-5.1577114273607783E-2</v>
       </c>
       <c r="AT47" s="24">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-1.7129661664766149E-2</v>
       </c>
       <c r="AU47" s="24">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-3.3572973393226402E-2</v>
       </c>
       <c r="AV47" s="24">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-3.2787401460882104E-2</v>
       </c>
       <c r="AW47" s="24">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-2.6614166627992875E-2</v>
       </c>
       <c r="AX47" s="24">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-2.1113855232532841E-2</v>
       </c>
       <c r="AY47" s="24">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-6.1393172789567241E-2</v>
       </c>
       <c r="AZ47" s="24">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-4.878241985136611E-2</v>
       </c>
       <c r="BA47" s="24">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-4.2640982790947746E-2</v>
       </c>
       <c r="BB47" s="24">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-3.6734510604613302E-2</v>
       </c>
       <c r="BC47" s="24">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-3.1097697580259598E-2</v>
       </c>
       <c r="BD47" s="24">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-0.19583428342773401</v>
       </c>
       <c r="BE47" s="24">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-5.0496845281010283E-2</v>
       </c>
       <c r="BF47" s="24">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-2.7251094551470012E-2</v>
       </c>
       <c r="BG47" s="24">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-2.0250553375030123E-2</v>
       </c>
       <c r="BH47" s="24">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-1.5242923407104203E-2</v>
       </c>
       <c r="BJ47" s="23" t="s">
@@ -9222,7 +9219,7 @@
       </c>
       <c r="BK47" s="13">
         <f>NPV(BK46,AS42:DJ42)+Main!J5-Main!J6</f>
-        <v>36704.626263306127</v>
+        <v>31399.326263306128</v>
       </c>
     </row>
     <row r="48" spans="2:147" x14ac:dyDescent="0.25">
@@ -9231,55 +9228,55 @@
       </c>
       <c r="I48" s="16"/>
       <c r="J48" s="16">
-        <f t="shared" ref="J48:O48" si="114">+J26/F26-1</f>
+        <f t="shared" ref="J48:O48" si="115">+J26/F26-1</f>
         <v>-4.6836982968369689E-2</v>
       </c>
       <c r="K48" s="16">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>-6.5741284984401127E-2</v>
       </c>
       <c r="L48" s="16">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>-8.103756708407861E-2</v>
       </c>
       <c r="M48" s="16">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>-0.11044112980006349</v>
       </c>
       <c r="N48" s="16">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>-0.1318716382532592</v>
       </c>
       <c r="O48" s="16">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>-0.15578570391521074</v>
       </c>
       <c r="P48" s="16">
-        <f t="shared" ref="P48:V48" si="115">+P26/L26-1</f>
+        <f t="shared" ref="P48:V48" si="116">+P26/L26-1</f>
         <v>-0.10380572318473802</v>
       </c>
       <c r="Q48" s="16">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>-8.1851077926711091E-2</v>
       </c>
       <c r="R48" s="16">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>-3.9957994224205651E-2</v>
       </c>
       <c r="S48" s="16">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>-2.7344645723458072E-2</v>
       </c>
       <c r="T48" s="16">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>3.0084170513168695E-2</v>
       </c>
       <c r="U48" s="16">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>-1.7818484596170081E-2</v>
       </c>
       <c r="V48" s="16">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>2.2970903522203656E-3</v>
       </c>
       <c r="W48" s="16"/>
@@ -9314,7 +9311,7 @@
       </c>
       <c r="BK48" s="17">
         <f>BK47/Main!J3</f>
-        <v>251.4015497486721</v>
+        <v>212.51084023666235</v>
       </c>
     </row>
     <row r="49" spans="2:60" x14ac:dyDescent="0.25">
@@ -9334,63 +9331,63 @@
         <v>0.82253155159613967</v>
       </c>
       <c r="H49" s="16">
-        <f t="shared" ref="H49" si="116">+H34/H32</f>
+        <f t="shared" ref="H49" si="117">+H34/H32</f>
         <v>0.83434234234234239</v>
       </c>
       <c r="I49" s="16">
-        <f t="shared" ref="I49:J49" si="117">+I34/I32</f>
+        <f t="shared" ref="I49:J49" si="118">+I34/I32</f>
         <v>0.8158264061319227</v>
       </c>
       <c r="J49" s="16">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0.7585677188105775</v>
       </c>
       <c r="K49" s="16">
-        <f t="shared" ref="K49:O49" si="118">+K34/K32</f>
+        <f t="shared" ref="K49:O49" si="119">+K34/K32</f>
         <v>0.70222766411248916</v>
       </c>
       <c r="L49" s="16">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>0.8130624541346414</v>
       </c>
       <c r="M49" s="16">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>0.81283635638827989</v>
       </c>
       <c r="N49" s="16">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>0.77558962264150932</v>
       </c>
       <c r="O49" s="16">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>0.73089727974015428</v>
       </c>
       <c r="P49" s="16">
-        <f t="shared" ref="P49:V49" si="119">+P34/P32</f>
+        <f t="shared" ref="P49:V49" si="120">+P34/P32</f>
         <v>0.75867263843648203</v>
       </c>
       <c r="Q49" s="16">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>0.73931944828676455</v>
       </c>
       <c r="R49" s="16">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>0.75409629971084946</v>
       </c>
       <c r="S49" s="16">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>0.78170705086225711</v>
       </c>
       <c r="T49" s="16">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>0.79565093918617391</v>
       </c>
       <c r="U49" s="16">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>0.75967231730067319</v>
       </c>
       <c r="V49" s="16">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>0.77981016010103066</v>
       </c>
       <c r="W49" s="16"/>
@@ -9400,31 +9397,31 @@
       <c r="AA49" s="16"/>
       <c r="AB49" s="16"/>
       <c r="AH49" s="18">
-        <f t="shared" ref="AH49:AL49" si="120">+AH34/AH32</f>
+        <f t="shared" ref="AH49:AL49" si="121">+AH34/AH32</f>
         <v>0.87931940679974852</v>
       </c>
       <c r="AI49" s="18">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.88476188706590619</v>
       </c>
       <c r="AJ49" s="18">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.87084235902452656</v>
       </c>
       <c r="AK49" s="18">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.86719787516600266</v>
       </c>
       <c r="AL49" s="18">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.86498821815370674</v>
       </c>
       <c r="AM49" s="18">
-        <f t="shared" ref="AM49:AN49" si="121">+AM34/AM32</f>
+        <f t="shared" ref="AM49:AN49" si="122">+AM34/AM32</f>
         <v>0.86399961051335739</v>
       </c>
       <c r="AN49" s="18">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.86573047915148083</v>
       </c>
       <c r="AO49" s="18">
@@ -9432,79 +9429,79 @@
         <v>0.80789473684210533</v>
       </c>
       <c r="AP49" s="18">
-        <f t="shared" ref="AP49:BH49" si="122">+AP34/AP32</f>
+        <f t="shared" ref="AP49:BH49" si="123">+AP34/AP32</f>
         <v>0.79359859397365506</v>
       </c>
       <c r="AQ49" s="18">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.82</v>
       </c>
       <c r="AR49" s="18">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.77916266187124716</v>
       </c>
       <c r="AS49" s="18">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.82</v>
       </c>
       <c r="AT49" s="18">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.82</v>
       </c>
       <c r="AU49" s="18">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.82</v>
       </c>
       <c r="AV49" s="18">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.82</v>
       </c>
       <c r="AW49" s="18">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.82</v>
       </c>
       <c r="AX49" s="18">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.82</v>
       </c>
       <c r="AY49" s="18">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.81999999999999984</v>
       </c>
       <c r="AZ49" s="18">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.81999999999999984</v>
       </c>
       <c r="BA49" s="18">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.82</v>
       </c>
       <c r="BB49" s="18">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.82</v>
       </c>
       <c r="BC49" s="18">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.82000000000000006</v>
       </c>
       <c r="BD49" s="18">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.82</v>
       </c>
       <c r="BE49" s="18">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.82</v>
       </c>
       <c r="BF49" s="18">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.82</v>
       </c>
       <c r="BG49" s="18">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.82</v>
       </c>
       <c r="BH49" s="18">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.82</v>
       </c>
     </row>
@@ -9837,23 +9834,23 @@
         <v>24598.399999999998</v>
       </c>
       <c r="P61" s="12">
-        <f t="shared" ref="P61:T61" si="123">SUM(P52:P60)</f>
+        <f t="shared" ref="P61:T61" si="124">SUM(P52:P60)</f>
         <v>0</v>
       </c>
       <c r="Q61" s="12">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0</v>
       </c>
       <c r="R61" s="12">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0</v>
       </c>
       <c r="S61" s="12">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0</v>
       </c>
       <c r="T61" s="12">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>26804.1</v>
       </c>
     </row>
@@ -10131,23 +10128,23 @@
         <v>24598.399999999998</v>
       </c>
       <c r="P71" s="12">
-        <f t="shared" ref="P71:T71" si="124">SUM(P63:P70)</f>
+        <f t="shared" ref="P71:T71" si="125">SUM(P63:P70)</f>
         <v>0</v>
       </c>
       <c r="Q71" s="12">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>0</v>
       </c>
       <c r="R71" s="12">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>0</v>
       </c>
       <c r="S71" s="12">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>0</v>
       </c>
       <c r="T71" s="12">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>26804.100000000002</v>
       </c>
       <c r="U71" s="12"/>
